--- a/business_surveys/017_retail_market_research_survey--business_surveys.xlsx
+++ b/business_surveys/017_retail_market_research_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>department_stores</t>
+          <t>department stores</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clothing_stores</t>
+          <t>clothing stores</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>electronics_stores</t>
+          <t>electronics stores</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>grocery_stores</t>
+          <t>grocery stores</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>home_goods_stores</t>
+          <t>home goods stores</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jewelry_stores</t>
+          <t>jewelry stores</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>other_stores</t>
+          <t>other stores</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vintage_stores</t>
+          <t>vintage stores</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18_24</t>
+          <t>18 24</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35_44</t>
+          <t>35 44</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45_54</t>
+          <t>45 54</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>65_plus</t>
+          <t>65 plus</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>department_stores</t>
+          <t>department stores</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>clothing_stores</t>
+          <t>clothing stores</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>electronics_stores</t>
+          <t>electronics stores</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>grocery_stores</t>
+          <t>grocery stores</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>home_goods_stores</t>
+          <t>home goods stores</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jewelry_stores</t>
+          <t>jewelry stores</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>other_stores</t>
+          <t>other stores</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>vintage_stores</t>
+          <t>vintage stores</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>prefer_not_to_say</t>
+          <t>prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>some_college</t>
+          <t>some college</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>self_employed</t>
+          <t>self employed</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>neither_satisfied_nor_dissatisfied</t>
+          <t>neither satisfied nor dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>in person</t>
         </is>
       </c>
     </row>
